--- a/fraud counts.xlsx
+++ b/fraud counts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sauchi/Desktop/Fraud Detect ML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABEBE6EA-C444-B34C-B26F-71711BF4A895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D52696B-B338-8144-A676-C6C1203076C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" xr2:uid="{B3A7C528-270C-834C-8A37-F6FAC6F8FD9F}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26600" xr2:uid="{B3A7C528-270C-834C-8A37-F6FAC6F8FD9F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="17">
   <si>
     <t>Date</t>
   </si>
@@ -63,13 +63,37 @@
   </si>
   <si>
     <t>Yes</t>
+  </si>
+  <si>
+    <t>mate25</t>
+  </si>
+  <si>
+    <t>Hsynymz</t>
+  </si>
+  <si>
+    <t>PIWIX_645cefefb1f77</t>
+  </si>
+  <si>
+    <t>pb_Sundeep001</t>
+  </si>
+  <si>
+    <t>O_eurzc4589450a</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>14 Features</t>
+  </si>
+  <si>
+    <t>14 features</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -81,6 +105,12 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -104,10 +134,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -442,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B0C140B-E9AE-4549-8CE8-694479885260}">
-  <dimension ref="D2:I5"/>
+  <dimension ref="C2:I20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="6" width="28.83203125" customWidth="1"/>
@@ -451,7 +482,7 @@
     <col min="9" max="9" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="4:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="3:9" x14ac:dyDescent="0.2">
       <c r="D2" t="s">
         <v>0</v>
       </c>
@@ -471,7 +502,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="4:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="3:9" x14ac:dyDescent="0.2">
       <c r="D3" s="1">
         <v>45698</v>
       </c>
@@ -481,7 +512,10 @@
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
     </row>
-    <row r="4" spans="4:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
       <c r="D4" s="1">
         <v>45699</v>
       </c>
@@ -501,7 +535,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="4:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="3:9" x14ac:dyDescent="0.2">
       <c r="F5" s="2" t="s">
         <v>7</v>
       </c>
@@ -510,6 +544,179 @@
       </c>
       <c r="H5">
         <v>0.57899999999999996</v>
+      </c>
+    </row>
+    <row r="9" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="1">
+        <v>45703</v>
+      </c>
+      <c r="E9" s="3">
+        <v>12</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="3">
+        <v>181093279</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0.91550845000000003</v>
+      </c>
+      <c r="I9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="E10" s="3"/>
+      <c r="F10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="3">
+        <v>181042198</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0.88938664999999995</v>
+      </c>
+      <c r="I10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="E11" s="3"/>
+      <c r="F11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="3">
+        <v>181038790</v>
+      </c>
+      <c r="H11" s="3">
+        <v>0.81973624</v>
+      </c>
+      <c r="I11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="E12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="3">
+        <v>181038607</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0.80131189999999997</v>
+      </c>
+      <c r="I12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="E13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="3">
+        <v>181043117</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0.79717159999999998</v>
+      </c>
+      <c r="I13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="E14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="3">
+        <v>181068578</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0.76562953</v>
+      </c>
+      <c r="I14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="E15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="3">
+        <v>181039062</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0.76273860000000004</v>
+      </c>
+      <c r="I15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="E16" s="3"/>
+      <c r="F16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="3">
+        <v>181038716</v>
+      </c>
+      <c r="H16" s="3">
+        <v>0.76267620000000003</v>
+      </c>
+    </row>
+    <row r="17" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="3">
+        <v>181042851</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0.74651825000000005</v>
+      </c>
+    </row>
+    <row r="18" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E18" s="3"/>
+      <c r="F18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="3">
+        <v>181038589</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0.70700353000000005</v>
+      </c>
+    </row>
+    <row r="19" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E19" s="3"/>
+      <c r="F19" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="3">
+        <v>181039841</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0.67037369999999996</v>
+      </c>
+    </row>
+    <row r="20" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E20" s="3"/>
+      <c r="F20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="3">
+        <v>181038857</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0.55708426</v>
       </c>
     </row>
   </sheetData>
